--- a/data/trans_dic/IP44C$alquiler_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,56</t>
+          <t>0,32; 4,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,87</t>
+          <t>0,34; 2,82</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,91</t>
+          <t>0,0; 7,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,16</t>
+          <t>0,91; 8,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,25</t>
+          <t>1,01; 5,85</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,01</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,47</t>
+          <t>0,0; 8,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,46</t>
+          <t>0,0; 4,94</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,96</t>
+          <t>0,0; 8,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 5,89</t>
+          <t>0,3; 5,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,37</t>
+          <t>0,67; 5,03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,64</t>
+          <t>0,67; 5,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,59</t>
+          <t>0,28; 4,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,63</t>
+          <t>0,79; 3,8</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,83</t>
+          <t>0,84; 5,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,53; 12,27</t>
+          <t>3,4; 11,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,71</t>
+          <t>2,71; 7,93</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,33</t>
+          <t>0,85; 2,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,74</t>
+          <t>1,61; 3,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,79</t>
+          <t>1,4; 2,68</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2232</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2648</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2215</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>407; 5911</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>860; 7117</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4110</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>599; 5323</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1223; 7118</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3162</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3446</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3453</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3694</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2073</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3970</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>166; 3239</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>678; 5089</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2713</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2287</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>805; 6604</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>420; 7331</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2153; 10308</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2991</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>10116</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1095; 6545</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>5180; 17761</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>7672; 22450</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>9450</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>18253</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>27703</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>5561; 15312</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>11953; 27301</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>19501; 37362</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$alquiler_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Provincia-trans_dic.xlsx
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,67</t>
+          <t>0,58; 5,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,82</t>
+          <t>0,35; 2,78</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,36</t>
+          <t>0,0; 7,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,1</t>
+          <t>0,91; 9,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,85</t>
+          <t>1,0; 5,47</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,59</t>
+          <t>0,0; 9,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,94</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,72</t>
+          <t>0,0; 8,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 5,82</t>
+          <t>0,3; 5,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,03</t>
+          <t>0,67; 5,19</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,52</t>
+          <t>0,67; 5,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,83</t>
+          <t>0,54; 4,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,8</t>
+          <t>0,76; 3,7</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,01</t>
+          <t>0,64; 5,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,4; 11,65</t>
+          <t>3,26; 12,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,93</t>
+          <t>2,55; 7,57</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,35</t>
+          <t>0,84; 2,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,67</t>
+          <t>1,54; 3,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,68</t>
+          <t>1,42; 2,72</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2215</t>
+          <t>0; 2678</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>407; 5911</t>
+          <t>728; 6802</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>860; 7117</t>
+          <t>877; 7033</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4110</t>
+          <t>0; 4082</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>599; 5323</t>
+          <t>601; 6570</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1223; 7118</t>
+          <t>1220; 6650</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3162</t>
+          <t>0; 3327</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3446</t>
+          <t>0; 3246</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3453</t>
+          <t>0; 3663</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3694</t>
+          <t>0; 3711</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3970</t>
+          <t>0; 3772</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>166; 3239</t>
+          <t>166; 3076</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>678; 5089</t>
+          <t>676; 5249</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>805; 6604</t>
+          <t>798; 6366</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>420; 7331</t>
+          <t>821; 6543</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2153; 10308</t>
+          <t>2049; 10027</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1095; 6545</t>
+          <t>833; 6834</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5180; 17761</t>
+          <t>4968; 18675</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7672; 22450</t>
+          <t>7216; 21444</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5561; 15312</t>
+          <t>5503; 14974</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>11953; 27301</t>
+          <t>11441; 27479</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19501; 37362</t>
+          <t>19836; 37938</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$alquiler_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,48; 5,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,37</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,78</t>
+          <t>0,31; 3,18</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,31</t>
+          <t>1,01; 9,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,99</t>
+          <t>0,0; 6,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,47</t>
+          <t>0,98; 6,15</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 8,46</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,11</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,29</t>
+          <t>0,51; 7,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 5,53</t>
+          <t>0,0; 9,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,19</t>
+          <t>1,0; 6,17</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,32</t>
+          <t>0,26; 5,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,31</t>
+          <t>0,86; 5,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,7</t>
+          <t>0,9; 3,85</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,23</t>
+          <t>3,18; 11,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,26; 12,25</t>
+          <t>0,62; 4,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,57</t>
+          <t>2,4; 7,03</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,3</t>
+          <t>1,55; 3,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,69</t>
+          <t>0,87; 2,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,72</t>
+          <t>1,48; 2,84</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>359</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2258</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2678</t>
+          <t>555; 6770</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>728; 6802</t>
+          <t>0; 1834</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>877; 7033</t>
+          <t>658; 6818</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3023</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4082</t>
+          <t>586; 5670</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>601; 6570</t>
+          <t>0; 3696</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1220; 6650</t>
+          <t>1106; 6911</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>826</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>826</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3327</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2827</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3246</t>
+          <t>0; 2769</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>651</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0; 3311</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3663</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3711</t>
+          <t>0; 3335</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2480</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3772</t>
+          <t>247; 3383</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>166; 3076</t>
+          <t>0; 4399</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>676; 5249</t>
+          <t>934; 5766</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4904</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>798; 6366</t>
+          <t>358; 7439</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>821; 6543</t>
+          <t>1015; 6604</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2049; 10027</t>
+          <t>2305; 9832</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>12219</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>833; 6834</t>
+          <t>4937; 17478</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4968; 18675</t>
+          <t>867; 6598</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7216; 21444</t>
+          <t>7069; 20729</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>17192</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>18253</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>26362</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5503; 14974</t>
+          <t>10614; 25844</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>11441; 27479</t>
+          <t>5391; 15045</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19836; 37938</t>
+          <t>19253; 36980</t>
         </is>
       </c>
     </row>
